--- a/ANILLOS SWA.xlsx
+++ b/ANILLOS SWA.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9891FC5D-C930-4F9C-A6E7-31FA57D178FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C482D8-A0A1-4532-905D-3E3530347B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
   <sheets>
     <sheet name="ANILLOS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="ANILLOS" localSheetId="0">ANILLOS!#REF!</definedName>
     <definedName name="ANILLOS">#REF!</definedName>
@@ -61,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t xml:space="preserve">ANILLOS </t>
   </si>
@@ -117,7 +114,7 @@
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +151,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -264,15 +268,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -311,8 +312,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,14 +339,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1009650" cy="1009650"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1209675</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1133475</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="image36.jpg">
@@ -367,15 +381,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1085850" cy="1085850"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1257300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1171575</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="image4.jpg">
@@ -405,15 +424,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1095375" cy="1095375"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1238250</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1190625</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="image10.jpg">
@@ -443,15 +467,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1095375" cy="1095375"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1266825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1162050</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="image5.jpg">
@@ -481,15 +510,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1057275" cy="1057275"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1219200</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1171575</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="image39.jpg">
@@ -519,15 +553,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1066800" cy="1066800"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1162050</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="image3.jpg">
@@ -557,15 +596,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1019175" cy="1019175"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1152525</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="image2.jpg">
@@ -595,15 +639,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1085850" cy="1085850"/>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1162050</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="image1.jpg">
@@ -633,31 +682,96 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>257176</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1314450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>987182</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0108612-9EBF-A4F8-8D57-A0F19DBE5E30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1628775" y="8648701"/>
+          <a:ext cx="1162050" cy="730006"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1142548</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737D57B3-D8F7-E446-273B-782F74F443C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1657350" y="7267575"/>
+          <a:ext cx="1047750" cy="999673"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="ANILLOS"/>
-      <sheetName val="ARETES"/>
-      <sheetName val="PULSERAS"/>
-      <sheetName val="COLLARES"/>
-      <sheetName val="SETS"/>
-      <sheetName val="TABLAS DE PESO"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -957,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:M748"/>
+  <dimension ref="A2:M750"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -974,417 +1088,483 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="28.5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="3"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="18.75">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.19</v>
-      </c>
-      <c r="G4" s="10">
-        <f t="shared" ref="G4:G11" si="0">D4+E4+F4</f>
-        <v>5.0000000000000009</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H11" si="1">G4*8</f>
-        <v>40.000000000000007</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I11" si="2">H4/0.95</f>
-        <v>42.105263157894747</v>
-      </c>
-      <c r="J4" s="11">
-        <f t="shared" ref="J4:J11" si="3">(I4*2)+5</f>
-        <v>89.210526315789494</v>
-      </c>
-      <c r="K4" s="11">
-        <v>90</v>
-      </c>
-      <c r="L4" s="12">
-        <f t="shared" ref="L4:L11" si="4">K4+10</f>
-        <v>100</v>
-      </c>
-      <c r="M4" s="13" t="s">
+      <c r="A4" s="2">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="17">
+        <v>9.33</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10">
+        <v>225</v>
+      </c>
+      <c r="M4" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" ref="G5" si="0">D5+E5+F5</f>
+        <v>5.0400000000000009</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" ref="H5:H13" si="1">G5*8</f>
+        <v>40.320000000000007</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" ref="I5:I13" si="2">H5/0.95</f>
+        <v>42.442105263157906</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" ref="J5:J13" si="3">(I5*2)+5</f>
+        <v>89.884210526315812</v>
+      </c>
+      <c r="K5" s="9">
+        <v>95</v>
+      </c>
+      <c r="L5" s="10">
+        <v>110</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A6" s="2">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5">
+        <v>11.9</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="G6" s="8">
+        <f t="shared" ref="G6:G13" si="4">D6+E6+F6</f>
+        <v>13.39</v>
+      </c>
+      <c r="H6" s="9">
+        <f t="shared" si="1"/>
+        <v>107.12</v>
+      </c>
+      <c r="I6" s="9">
+        <f t="shared" si="2"/>
+        <v>112.75789473684212</v>
+      </c>
+      <c r="J6" s="9">
+        <f t="shared" si="3"/>
+        <v>230.51578947368424</v>
+      </c>
+      <c r="K6" s="9">
+        <v>230</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" ref="L6:L13" si="5">K6+10</f>
+        <v>240</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5">
+        <v>7.64</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="4"/>
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="H7" s="9">
+        <f t="shared" si="1"/>
+        <v>68.239999999999995</v>
+      </c>
+      <c r="I7" s="9">
+        <f t="shared" si="2"/>
+        <v>71.831578947368413</v>
+      </c>
+      <c r="J7" s="9">
+        <f t="shared" si="3"/>
+        <v>148.66315789473683</v>
+      </c>
+      <c r="K7" s="9">
+        <v>150</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="5"/>
+        <v>160</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>40</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.9</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" si="4"/>
+        <v>10.51</v>
+      </c>
+      <c r="H8" s="9">
+        <f t="shared" si="1"/>
+        <v>84.08</v>
+      </c>
+      <c r="I8" s="9">
+        <f t="shared" si="2"/>
+        <v>88.505263157894746</v>
+      </c>
+      <c r="J8" s="9">
+        <f t="shared" si="3"/>
+        <v>182.01052631578949</v>
+      </c>
+      <c r="K8" s="9">
+        <v>185</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="5"/>
+        <v>195</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H9" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J9" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K9" s="9">
+        <v>95</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A10" s="2">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H10" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J10" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K10" s="9">
+        <v>95</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A11" s="2">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="4"/>
+        <v>9.57</v>
+      </c>
+      <c r="H11" s="9">
+        <f t="shared" si="1"/>
+        <v>76.56</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="2"/>
+        <v>80.589473684210532</v>
+      </c>
+      <c r="J11" s="9">
+        <f t="shared" si="3"/>
+        <v>166.17894736842106</v>
+      </c>
+      <c r="K11" s="9">
+        <v>170</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B12" s="3">
         <v>15</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7">
+      <c r="C12" s="4"/>
+      <c r="D12" s="5">
         <v>4.1100000000000003</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E12" s="6">
         <v>0.7</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F12" s="7">
         <v>0.19</v>
       </c>
-      <c r="G5" s="10">
-        <f t="shared" si="0"/>
+      <c r="G12" s="8">
+        <f t="shared" si="4"/>
         <v>5.0000000000000009</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H12" s="9">
         <f t="shared" si="1"/>
         <v>40.000000000000007</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I12" s="9">
         <f t="shared" si="2"/>
         <v>42.105263157894747</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J12" s="9">
         <f t="shared" si="3"/>
         <v>89.210526315789494</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K12" s="9">
         <v>90</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L12" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A13" s="2">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G13" s="8">
         <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K13" s="9">
+        <v>90</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M13" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7">
-        <v>8.08</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1.17</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0.32</v>
-      </c>
-      <c r="G6" s="10">
-        <f t="shared" si="0"/>
-        <v>9.57</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="1"/>
-        <v>76.56</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="2"/>
-        <v>80.589473684210532</v>
-      </c>
-      <c r="J6" s="11">
-        <f t="shared" si="3"/>
-        <v>166.17894736842106</v>
-      </c>
-      <c r="K6" s="11">
-        <v>170</v>
-      </c>
-      <c r="L6" s="12">
-        <f t="shared" si="4"/>
-        <v>180</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7">
-        <v>4.41</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="F7" s="9">
-        <v>0.19</v>
-      </c>
-      <c r="G7" s="10">
-        <f t="shared" si="0"/>
-        <v>5.3000000000000007</v>
-      </c>
-      <c r="H7" s="11">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
-      </c>
-      <c r="I7" s="11">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
-      </c>
-      <c r="J7" s="11">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
-      </c>
-      <c r="K7" s="11">
-        <v>95</v>
-      </c>
-      <c r="L7" s="12">
-        <f t="shared" si="4"/>
-        <v>105</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7">
-        <v>4.41</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0.19</v>
-      </c>
-      <c r="G8" s="10">
-        <f t="shared" si="0"/>
-        <v>5.3000000000000007</v>
-      </c>
-      <c r="H8" s="11">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
-      </c>
-      <c r="I8" s="11">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
-      </c>
-      <c r="J8" s="11">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
-      </c>
-      <c r="K8" s="11">
-        <v>95</v>
-      </c>
-      <c r="L8" s="12">
-        <f t="shared" si="4"/>
-        <v>105</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5">
-        <v>40</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7">
-        <v>8.08</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.9</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0.53</v>
-      </c>
-      <c r="G9" s="10">
-        <f t="shared" si="0"/>
-        <v>10.51</v>
-      </c>
-      <c r="H9" s="11">
-        <f t="shared" si="1"/>
-        <v>84.08</v>
-      </c>
-      <c r="I9" s="11">
-        <f t="shared" si="2"/>
-        <v>88.505263157894746</v>
-      </c>
-      <c r="J9" s="11">
-        <f t="shared" si="3"/>
-        <v>182.01052631578949</v>
-      </c>
-      <c r="K9" s="11">
-        <v>185</v>
-      </c>
-      <c r="L9" s="12">
-        <f t="shared" si="4"/>
-        <v>195</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5">
-        <v>15</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7">
-        <v>7.64</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0.19</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" si="0"/>
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="1"/>
-        <v>68.239999999999995</v>
-      </c>
-      <c r="I10" s="11">
-        <f t="shared" si="2"/>
-        <v>71.831578947368413</v>
-      </c>
-      <c r="J10" s="11">
-        <f t="shared" si="3"/>
-        <v>148.66315789473683</v>
-      </c>
-      <c r="K10" s="11">
-        <v>150</v>
-      </c>
-      <c r="L10" s="12">
-        <f t="shared" si="4"/>
-        <v>160</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5">
-        <v>25</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.17</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0.32</v>
-      </c>
-      <c r="G11" s="10">
-        <f t="shared" si="0"/>
-        <v>13.39</v>
-      </c>
-      <c r="H11" s="11">
-        <f t="shared" si="1"/>
-        <v>107.12</v>
-      </c>
-      <c r="I11" s="11">
-        <f t="shared" si="2"/>
-        <v>112.75789473684212</v>
-      </c>
-      <c r="J11" s="11">
-        <f t="shared" si="3"/>
-        <v>230.51578947368424</v>
-      </c>
-      <c r="K11" s="11">
-        <v>230</v>
-      </c>
-      <c r="L11" s="12">
-        <f t="shared" si="4"/>
-        <v>240</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="14" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="15" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="16" spans="1:13" ht="15.75" customHeight="1"/>
@@ -2120,18 +2300,25 @@
     <row r="746" ht="15.75" customHeight="1"/>
     <row r="747" ht="15.75" customHeight="1"/>
     <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:M13">
+    <sortCondition descending="1" ref="A6:A13"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D10" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
-    <hyperlink ref="D11" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
+    <hyperlink ref="D13" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D7" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
+    <hyperlink ref="D6" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
+    <hyperlink ref="D4" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
-  <drawing r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
--- a/ANILLOS SWA.xlsx
+++ b/ANILLOS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C482D8-A0A1-4532-905D-3E3530347B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1F2B63-D50E-48F3-BF71-F1D40A2C46BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
   <si>
     <t xml:space="preserve">ANILLOS </t>
   </si>
@@ -312,13 +312,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -343,13 +343,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1209675</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1133475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -386,13 +386,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1257300</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -429,13 +429,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -472,13 +472,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -515,13 +515,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -558,13 +558,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -601,13 +601,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -644,13 +644,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -687,13 +687,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>257176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>987182</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -731,13 +731,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1142548</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -763,6 +763,226 @@
         <a:xfrm>
           <a:off x="1657350" y="7267575"/>
           <a:ext cx="1047750" cy="999673"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1219200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>995408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C75896F1-FA54-513F-5E1A-7A7595608CF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1695450" y="1028700"/>
+          <a:ext cx="1000125" cy="757283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>295276</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1343026</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1103688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Imagen 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D78683B-722B-C410-2BBA-A93225B93480}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1581151" y="1085851"/>
+          <a:ext cx="1238250" cy="808412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1290246</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1152525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Imagen 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B973EAF3-457B-2B97-008E-D75A02AA6683}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1647825" y="1123950"/>
+          <a:ext cx="1118796" cy="819150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>276224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1362813</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1104899</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Imagen 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2FEB4D2-7165-1F19-0285-FBD36C4591D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1619250" y="1066799"/>
+          <a:ext cx="1219938" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95251</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1333501</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1000125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Imagen 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87AC0CC4-72F2-8DF3-4A3A-C03FFEEFDC57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1571626" y="1047750"/>
+          <a:ext cx="1238250" cy="742950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1071,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:M750"/>
+  <dimension ref="A2:M755"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1088,20 +1308,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="28.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="18.75">
@@ -1147,14 +1367,14 @@
     </row>
     <row r="4" spans="1:13" ht="99.75" customHeight="1">
       <c r="A4" s="2">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
-        <v>20</v>
-      </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="17">
-        <v>9.33</v>
+      <c r="D4" s="15">
+        <v>4.1500000000000004</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="7"/>
@@ -1164,7 +1384,7 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="10">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>12</v>
@@ -1172,40 +1392,22 @@
     </row>
     <row r="5" spans="1:13" ht="99.75" customHeight="1">
       <c r="A5" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3">
         <v>10</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="17">
+      <c r="D5" s="15">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E5" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" ref="G5" si="0">D5+E5+F5</f>
-        <v>5.0400000000000009</v>
-      </c>
-      <c r="H5" s="9">
-        <f t="shared" ref="H5:H13" si="1">G5*8</f>
-        <v>40.320000000000007</v>
-      </c>
-      <c r="I5" s="9">
-        <f t="shared" ref="I5:I13" si="2">H5/0.95</f>
-        <v>42.442105263157906</v>
-      </c>
-      <c r="J5" s="9">
-        <f t="shared" ref="J5:J13" si="3">(I5*2)+5</f>
-        <v>89.884210526315812</v>
-      </c>
-      <c r="K5" s="9">
-        <v>95</v>
-      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
       <c r="L5" s="10">
         <v>110</v>
       </c>
@@ -1215,43 +1417,24 @@
     </row>
     <row r="6" spans="1:13" ht="99.75" customHeight="1">
       <c r="A6" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="5">
-        <v>11.9</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="G6" s="8">
-        <f t="shared" ref="G6:G13" si="4">D6+E6+F6</f>
-        <v>13.39</v>
-      </c>
-      <c r="H6" s="9">
-        <f t="shared" si="1"/>
-        <v>107.12</v>
-      </c>
-      <c r="I6" s="9">
-        <f t="shared" si="2"/>
-        <v>112.75789473684212</v>
-      </c>
-      <c r="J6" s="9">
-        <f t="shared" si="3"/>
-        <v>230.51578947368424</v>
-      </c>
-      <c r="K6" s="9">
-        <v>230</v>
-      </c>
+      <c r="D6" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <f t="shared" ref="L6:L13" si="5">K6+10</f>
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>12</v>
@@ -1259,43 +1442,24 @@
     </row>
     <row r="7" spans="1:13" ht="99.75" customHeight="1">
       <c r="A7" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="5">
-        <v>7.64</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G7" s="8">
-        <f t="shared" si="4"/>
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="H7" s="9">
-        <f t="shared" si="1"/>
-        <v>68.239999999999995</v>
-      </c>
-      <c r="I7" s="9">
-        <f t="shared" si="2"/>
-        <v>71.831578947368413</v>
-      </c>
-      <c r="J7" s="9">
-        <f t="shared" si="3"/>
-        <v>148.66315789473683</v>
-      </c>
-      <c r="K7" s="9">
-        <v>150</v>
-      </c>
+      <c r="D7" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <f t="shared" si="5"/>
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>12</v>
@@ -1303,43 +1467,24 @@
     </row>
     <row r="8" spans="1:13" ht="99.75" customHeight="1">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="5">
-        <v>8.08</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="G8" s="8">
-        <f t="shared" si="4"/>
-        <v>10.51</v>
-      </c>
-      <c r="H8" s="9">
-        <f t="shared" si="1"/>
-        <v>84.08</v>
-      </c>
-      <c r="I8" s="9">
-        <f t="shared" si="2"/>
-        <v>88.505263157894746</v>
-      </c>
-      <c r="J8" s="9">
-        <f t="shared" si="3"/>
-        <v>182.01052631578949</v>
-      </c>
-      <c r="K8" s="9">
-        <v>185</v>
-      </c>
+      <c r="D8" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="10">
-        <f t="shared" si="5"/>
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>12</v>
@@ -1347,43 +1492,24 @@
     </row>
     <row r="9" spans="1:13" ht="99.75" customHeight="1">
       <c r="A9" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="5">
-        <v>4.41</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
-      </c>
-      <c r="H9" s="9">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
-      </c>
-      <c r="I9" s="9">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
-      </c>
-      <c r="J9" s="9">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
-      </c>
-      <c r="K9" s="9">
-        <v>95</v>
-      </c>
+      <c r="D9" s="15">
+        <v>9.33</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
       <c r="L9" s="10">
-        <f t="shared" si="5"/>
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>12</v>
@@ -1391,14 +1517,14 @@
     </row>
     <row r="10" spans="1:13" ht="99.75" customHeight="1">
       <c r="A10" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="5">
-        <v>4.41</v>
+      <c r="D10" s="15">
+        <v>4.1500000000000004</v>
       </c>
       <c r="E10" s="6">
         <v>0.7</v>
@@ -1407,27 +1533,26 @@
         <v>0.19</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
+        <f t="shared" ref="G10" si="0">D10+E10+F10</f>
+        <v>5.0400000000000009</v>
       </c>
       <c r="H10" s="9">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
+        <f t="shared" ref="H10:H18" si="1">G10*8</f>
+        <v>40.320000000000007</v>
       </c>
       <c r="I10" s="9">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
+        <f t="shared" ref="I10:I18" si="2">H10/0.95</f>
+        <v>42.442105263157906</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
+        <f t="shared" ref="J10:J18" si="3">(I10*2)+5</f>
+        <v>89.884210526315812</v>
       </c>
       <c r="K10" s="9">
         <v>95</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="5"/>
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>12</v>
@@ -1435,14 +1560,14 @@
     </row>
     <row r="11" spans="1:13" ht="99.75" customHeight="1">
       <c r="A11" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B11" s="3">
         <v>25</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="5">
-        <v>8.08</v>
+        <v>11.9</v>
       </c>
       <c r="E11" s="6">
         <v>1.17</v>
@@ -1451,27 +1576,27 @@
         <v>0.32</v>
       </c>
       <c r="G11" s="8">
-        <f t="shared" si="4"/>
-        <v>9.57</v>
+        <f t="shared" ref="G11:G18" si="4">D11+E11+F11</f>
+        <v>13.39</v>
       </c>
       <c r="H11" s="9">
         <f t="shared" si="1"/>
-        <v>76.56</v>
+        <v>107.12</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>80.589473684210532</v>
+        <v>112.75789473684212</v>
       </c>
       <c r="J11" s="9">
         <f t="shared" si="3"/>
-        <v>166.17894736842106</v>
+        <v>230.51578947368424</v>
       </c>
       <c r="K11" s="9">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="L11" s="10">
-        <f t="shared" si="5"/>
-        <v>180</v>
+        <f t="shared" ref="L11:L18" si="5">K11+10</f>
+        <v>240</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>12</v>
@@ -1479,14 +1604,14 @@
     </row>
     <row r="12" spans="1:13" ht="99.75" customHeight="1">
       <c r="A12" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B12" s="3">
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="5">
-        <v>4.1100000000000003</v>
+        <v>7.64</v>
       </c>
       <c r="E12" s="6">
         <v>0.7</v>
@@ -1496,26 +1621,26 @@
       </c>
       <c r="G12" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="H12" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>68.239999999999995</v>
       </c>
       <c r="I12" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>71.831578947368413</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>148.66315789473683</v>
       </c>
       <c r="K12" s="9">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="L12" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>12</v>
@@ -1523,67 +1648,282 @@
     </row>
     <row r="13" spans="1:13" ht="99.75" customHeight="1">
       <c r="A13" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="5">
-        <v>4.1100000000000003</v>
+        <v>8.08</v>
       </c>
       <c r="E13" s="6">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F13" s="7">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>10.51</v>
       </c>
       <c r="H13" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>84.08</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>88.505263157894746</v>
       </c>
       <c r="J13" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>182.01052631578949</v>
       </c>
       <c r="K13" s="9">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="L13" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A14" s="2">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H14" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J14" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K14" s="9">
+        <v>95</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A15" s="2">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H15" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K15" s="9">
+        <v>95</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A16" s="2">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="4"/>
+        <v>9.57</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="1"/>
+        <v>76.56</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="2"/>
+        <v>80.589473684210532</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="3"/>
+        <v>166.17894736842106</v>
+      </c>
+      <c r="K16" s="9">
+        <v>170</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A17" s="2">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H17" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I17" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J17" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K17" s="9">
+        <v>90</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A18" s="2">
+        <v>1</v>
+      </c>
+      <c r="B18" s="3">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K18" s="9">
+        <v>90</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2302,23 +2642,33 @@
     <row r="748" ht="15.75" customHeight="1"/>
     <row r="749" ht="15.75" customHeight="1"/>
     <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:M13">
-    <sortCondition descending="1" ref="A6:A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:M18">
+    <sortCondition descending="1" ref="A11:A18"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D13" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D7" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
-    <hyperlink ref="D6" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
-    <hyperlink ref="D4" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
+    <hyperlink ref="D18" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D12" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
+    <hyperlink ref="D11" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
+    <hyperlink ref="D10" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
+    <hyperlink ref="D9" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
+    <hyperlink ref="D8" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
+    <hyperlink ref="D7" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
+    <hyperlink ref="D6" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
+    <hyperlink ref="D5" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
+    <hyperlink ref="D4" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/ANILLOS SWA.xlsx
+++ b/ANILLOS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1F2B63-D50E-48F3-BF71-F1D40A2C46BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDBB34B-3F06-42E3-A680-19BCBAC4C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
   <si>
     <t xml:space="preserve">ANILLOS </t>
   </si>
@@ -343,13 +343,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1209675</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>1133475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -386,13 +386,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1257300</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -429,13 +429,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -472,13 +472,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -515,13 +515,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -558,13 +558,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -601,13 +601,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -644,13 +644,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -687,13 +687,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>257176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>987182</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -731,13 +731,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1142548</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -775,13 +775,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>995408</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -819,13 +819,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>295276</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343026</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1103688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -863,13 +863,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1290246</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -907,13 +907,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>276224</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362813</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1104899</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -951,13 +951,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1333501</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1000125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -983,6 +983,226 @@
         <a:xfrm>
           <a:off x="1571626" y="1047750"/>
           <a:ext cx="1238250" cy="742950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1355961</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1104900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68BDBB43-FAB1-8428-3E36-18C96D06BB02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="6191250"/>
+          <a:ext cx="1289286" cy="771525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1303022</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67A8F607-60EF-4EFE-78E5-048DDB4A0FA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1581151" y="4895850"/>
+          <a:ext cx="1198246" cy="752475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>314326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1333501</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1083688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Imagen 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2B708F2-ED66-3239-7AC9-2B9C6A2CAB17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552576" y="3638551"/>
+          <a:ext cx="1257300" cy="769362"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85726</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1304926</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>910771</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Imagen 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072E9A4-B360-7595-3852-4C828A04C798}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1562101" y="2286000"/>
+          <a:ext cx="1219200" cy="682171"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1314450</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>981613</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Imagen 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE700249-57AB-8E08-4E14-1032AB7D0D36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1581150" y="1047750"/>
+          <a:ext cx="1209675" cy="724438"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1291,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:M755"/>
+  <dimension ref="A2:M760"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1367,7 +1587,7 @@
     </row>
     <row r="4" spans="1:13" ht="99.75" customHeight="1">
       <c r="A4" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
@@ -1392,7 +1612,7 @@
     </row>
     <row r="5" spans="1:13" ht="99.75" customHeight="1">
       <c r="A5" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3">
         <v>10</v>
@@ -1417,14 +1637,14 @@
     </row>
     <row r="6" spans="1:13" ht="99.75" customHeight="1">
       <c r="A6" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1434,7 +1654,7 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>12</v>
@@ -1442,14 +1662,14 @@
     </row>
     <row r="7" spans="1:13" ht="99.75" customHeight="1">
       <c r="A7" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -1459,7 +1679,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>12</v>
@@ -1467,14 +1687,14 @@
     </row>
     <row r="8" spans="1:13" ht="99.75" customHeight="1">
       <c r="A8" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -1484,7 +1704,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>12</v>
@@ -1492,14 +1712,14 @@
     </row>
     <row r="9" spans="1:13" ht="99.75" customHeight="1">
       <c r="A9" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3">
         <v>10</v>
-      </c>
-      <c r="B9" s="3">
-        <v>20</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="15">
-        <v>9.33</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
@@ -1509,7 +1729,7 @@
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="10">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>12</v>
@@ -1517,7 +1737,7 @@
     </row>
     <row r="10" spans="1:13" ht="99.75" customHeight="1">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
@@ -1526,31 +1746,13 @@
       <c r="D10" s="15">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E10" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G10" s="8">
-        <f t="shared" ref="G10" si="0">D10+E10+F10</f>
-        <v>5.0400000000000009</v>
-      </c>
-      <c r="H10" s="9">
-        <f t="shared" ref="H10:H18" si="1">G10*8</f>
-        <v>40.320000000000007</v>
-      </c>
-      <c r="I10" s="9">
-        <f t="shared" ref="I10:I18" si="2">H10/0.95</f>
-        <v>42.442105263157906</v>
-      </c>
-      <c r="J10" s="9">
-        <f t="shared" ref="J10:J18" si="3">(I10*2)+5</f>
-        <v>89.884210526315812</v>
-      </c>
-      <c r="K10" s="9">
-        <v>95</v>
-      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
       <c r="L10" s="10">
         <v>110</v>
       </c>
@@ -1560,43 +1762,24 @@
     </row>
     <row r="11" spans="1:13" ht="99.75" customHeight="1">
       <c r="A11" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="5">
-        <v>11.9</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" ref="G11:G18" si="4">D11+E11+F11</f>
-        <v>13.39</v>
-      </c>
-      <c r="H11" s="9">
-        <f t="shared" si="1"/>
-        <v>107.12</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="2"/>
-        <v>112.75789473684212</v>
-      </c>
-      <c r="J11" s="9">
-        <f t="shared" si="3"/>
-        <v>230.51578947368424</v>
-      </c>
-      <c r="K11" s="9">
-        <v>230</v>
-      </c>
+      <c r="D11" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
       <c r="L11" s="10">
-        <f t="shared" ref="L11:L18" si="5">K11+10</f>
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>12</v>
@@ -1604,43 +1787,24 @@
     </row>
     <row r="12" spans="1:13" ht="99.75" customHeight="1">
       <c r="A12" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="5">
-        <v>7.64</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="4"/>
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="H12" s="9">
-        <f t="shared" si="1"/>
-        <v>68.239999999999995</v>
-      </c>
-      <c r="I12" s="9">
-        <f t="shared" si="2"/>
-        <v>71.831578947368413</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="3"/>
-        <v>148.66315789473683</v>
-      </c>
-      <c r="K12" s="9">
-        <v>150</v>
-      </c>
+      <c r="D12" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="10">
-        <f t="shared" si="5"/>
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>12</v>
@@ -1648,43 +1812,24 @@
     </row>
     <row r="13" spans="1:13" ht="99.75" customHeight="1">
       <c r="A13" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="5">
-        <v>8.08</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="F13" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="4"/>
-        <v>10.51</v>
-      </c>
-      <c r="H13" s="9">
-        <f t="shared" si="1"/>
-        <v>84.08</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="2"/>
-        <v>88.505263157894746</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="3"/>
-        <v>182.01052631578949</v>
-      </c>
-      <c r="K13" s="9">
-        <v>185</v>
-      </c>
+      <c r="D13" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
       <c r="L13" s="10">
-        <f t="shared" si="5"/>
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>12</v>
@@ -1692,43 +1837,24 @@
     </row>
     <row r="14" spans="1:13" ht="99.75" customHeight="1">
       <c r="A14" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="5">
-        <v>4.41</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
-      </c>
-      <c r="H14" s="9">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
-      </c>
-      <c r="J14" s="9">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
-      </c>
-      <c r="K14" s="9">
-        <v>95</v>
-      </c>
+      <c r="D14" s="15">
+        <v>9.33</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
       <c r="L14" s="10">
-        <f t="shared" si="5"/>
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>12</v>
@@ -1736,14 +1862,14 @@
     </row>
     <row r="15" spans="1:13" ht="99.75" customHeight="1">
       <c r="A15" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B15" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="5">
-        <v>4.41</v>
+      <c r="D15" s="15">
+        <v>4.1500000000000004</v>
       </c>
       <c r="E15" s="6">
         <v>0.7</v>
@@ -1752,27 +1878,26 @@
         <v>0.19</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
+        <f t="shared" ref="G15" si="0">D15+E15+F15</f>
+        <v>5.0400000000000009</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
+        <f t="shared" ref="H15:H23" si="1">G15*8</f>
+        <v>40.320000000000007</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
+        <f t="shared" ref="I15:I23" si="2">H15/0.95</f>
+        <v>42.442105263157906</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
+        <f t="shared" ref="J15:J23" si="3">(I15*2)+5</f>
+        <v>89.884210526315812</v>
       </c>
       <c r="K15" s="9">
         <v>95</v>
       </c>
       <c r="L15" s="10">
-        <f t="shared" si="5"/>
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>12</v>
@@ -1780,14 +1905,14 @@
     </row>
     <row r="16" spans="1:13" ht="99.75" customHeight="1">
       <c r="A16" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B16" s="3">
         <v>25</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5">
-        <v>8.08</v>
+        <v>11.9</v>
       </c>
       <c r="E16" s="6">
         <v>1.17</v>
@@ -1796,27 +1921,27 @@
         <v>0.32</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="4"/>
-        <v>9.57</v>
+        <f t="shared" ref="G16:G23" si="4">D16+E16+F16</f>
+        <v>13.39</v>
       </c>
       <c r="H16" s="9">
         <f t="shared" si="1"/>
-        <v>76.56</v>
+        <v>107.12</v>
       </c>
       <c r="I16" s="9">
         <f t="shared" si="2"/>
-        <v>80.589473684210532</v>
+        <v>112.75789473684212</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="3"/>
-        <v>166.17894736842106</v>
+        <v>230.51578947368424</v>
       </c>
       <c r="K16" s="9">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="L16" s="10">
-        <f t="shared" si="5"/>
-        <v>180</v>
+        <f t="shared" ref="L16:L23" si="5">K16+10</f>
+        <v>240</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>12</v>
@@ -1824,14 +1949,14 @@
     </row>
     <row r="17" spans="1:13" ht="99.75" customHeight="1">
       <c r="A17" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3">
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="5">
-        <v>4.1100000000000003</v>
+        <v>7.64</v>
       </c>
       <c r="E17" s="6">
         <v>0.7</v>
@@ -1841,26 +1966,26 @@
       </c>
       <c r="G17" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="H17" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>68.239999999999995</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>71.831578947368413</v>
       </c>
       <c r="J17" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>148.66315789473683</v>
       </c>
       <c r="K17" s="9">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="L17" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>12</v>
@@ -1868,53 +1993,268 @@
     </row>
     <row r="18" spans="1:13" ht="99.75" customHeight="1">
       <c r="A18" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B18" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="5">
-        <v>4.1100000000000003</v>
+        <v>8.08</v>
       </c>
       <c r="E18" s="6">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F18" s="7">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>10.51</v>
       </c>
       <c r="H18" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>84.08</v>
       </c>
       <c r="I18" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>88.505263157894746</v>
       </c>
       <c r="J18" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>182.01052631578949</v>
       </c>
       <c r="K18" s="9">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="L18" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="20" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="19" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A19" s="2">
+        <v>5</v>
+      </c>
+      <c r="B19" s="3">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H19" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K19" s="9">
+        <v>95</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A20" s="2">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G20" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K20" s="9">
+        <v>95</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A21" s="2">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="4"/>
+        <v>9.57</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="1"/>
+        <v>76.56</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="2"/>
+        <v>80.589473684210532</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="3"/>
+        <v>166.17894736842106</v>
+      </c>
+      <c r="K21" s="9">
+        <v>170</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A22" s="2">
+        <v>2</v>
+      </c>
+      <c r="B22" s="3">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K22" s="9">
+        <v>90</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A23" s="2">
+        <v>1</v>
+      </c>
+      <c r="B23" s="3">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K23" s="9">
+        <v>90</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="25" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="26" spans="1:13" ht="15.75" customHeight="1"/>
@@ -2647,28 +2987,38 @@
     <row r="753" ht="15.75" customHeight="1"/>
     <row r="754" ht="15.75" customHeight="1"/>
     <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:M18">
-    <sortCondition descending="1" ref="A11:A18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:M23">
+    <sortCondition descending="1" ref="A16:A23"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D18" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D12" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
-    <hyperlink ref="D11" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
-    <hyperlink ref="D10" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
-    <hyperlink ref="D9" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
-    <hyperlink ref="D8" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
-    <hyperlink ref="D7" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
-    <hyperlink ref="D6" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
-    <hyperlink ref="D5" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
-    <hyperlink ref="D4" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
+    <hyperlink ref="D23" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D17" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
+    <hyperlink ref="D16" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
+    <hyperlink ref="D15" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
+    <hyperlink ref="D14" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
+    <hyperlink ref="D13" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
+    <hyperlink ref="D12" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
+    <hyperlink ref="D11" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
+    <hyperlink ref="D10" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
+    <hyperlink ref="D9" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
+    <hyperlink ref="D8" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{8C8268C3-6698-451E-835B-5881BC24A1E5}"/>
+    <hyperlink ref="D7" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7798C588-14D3-4699-9A26-5CD4BF185816}"/>
+    <hyperlink ref="D6" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1EB97EDE-E1FA-475A-A341-8A2E05CA1DC0}"/>
+    <hyperlink ref="D5" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FAE6B8A7-EF45-4233-B6B0-CC5A22CEFD2F}"/>
+    <hyperlink ref="D4" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{AB1BE585-CA32-4BAF-9B9B-D69C1EE9D872}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
-  <drawing r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
--- a/ANILLOS SWA.xlsx
+++ b/ANILLOS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDBB34B-3F06-42E3-A680-19BCBAC4C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F1C38B-AE0E-4C1F-99D1-798E61D465A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -1654,7 +1654,7 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>12</v>
@@ -1679,7 +1679,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>12</v>

--- a/ANILLOS SWA.xlsx
+++ b/ANILLOS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F1C38B-AE0E-4C1F-99D1-798E61D465A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62177D47-6C0C-4C55-855F-C9CDF7B34A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
   <si>
     <t xml:space="preserve">ANILLOS </t>
   </si>
@@ -343,13 +343,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1209675</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>1133475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -386,13 +386,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1257300</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -429,13 +429,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -472,13 +472,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -515,13 +515,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -558,13 +558,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -601,13 +601,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -644,13 +644,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -687,13 +687,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>257176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>987182</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -731,13 +731,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1142548</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -775,13 +775,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>995408</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -819,13 +819,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>295276</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343026</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1103688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -863,13 +863,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1290246</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -907,13 +907,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>276224</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362813</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1104899</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -951,13 +951,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1333501</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1000125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -995,13 +995,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1355961</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1104900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1039,13 +1039,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1303022</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1083,13 +1083,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>314326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1333501</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1083688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1127,13 +1127,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85726</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304926</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>910771</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1171,13 +1171,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>981613</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1203,6 +1203,226 @@
         <a:xfrm>
           <a:off x="1581150" y="1047750"/>
           <a:ext cx="1209675" cy="724438"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>166450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1085850</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1200944</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Imagen 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A22AEC75-A9DE-5DD4-428E-858F57A9F1B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1771650" y="6024325"/>
+          <a:ext cx="790575" cy="1034494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323851</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1090589</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1200958</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Imagen 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B69CE12C-62A5-3056-CCA7-C91E5634BE0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1800226" y="4705350"/>
+          <a:ext cx="766738" cy="1086658"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>220979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1005887</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Imagen 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{245B861F-672F-E4EB-6DF6-04D06748CBDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1628775" y="3545204"/>
+          <a:ext cx="1143000" cy="784908"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1304925</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1065262</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Imagen 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D021756B-F2A6-67B8-AC30-965AC69994CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1590676" y="2305050"/>
+          <a:ext cx="1190624" cy="817612"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>352426</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1009982</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1200870</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Imagen 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAF28D2D-4AA8-CE95-D986-75CD7860B9F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828801" y="904874"/>
+          <a:ext cx="657556" cy="1086571"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1511,7 +1731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:M760"/>
+  <dimension ref="A2:M765"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1587,14 +1807,14 @@
     </row>
     <row r="4" spans="1:13" ht="99.75" customHeight="1">
       <c r="A4" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="15">
-        <v>4.1500000000000004</v>
+        <v>3.41</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="7"/>
@@ -1604,7 +1824,7 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="10">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>12</v>
@@ -1612,14 +1832,14 @@
     </row>
     <row r="5" spans="1:13" ht="99.75" customHeight="1">
       <c r="A5" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>10</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="15">
-        <v>4.1500000000000004</v>
+        <v>5.48</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1629,7 +1849,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="10">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>12</v>
@@ -1637,14 +1857,14 @@
     </row>
     <row r="6" spans="1:13" ht="99.75" customHeight="1">
       <c r="A6" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="15">
-        <v>4.1500000000000004</v>
+        <v>5.48</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1654,7 +1874,7 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>12</v>
@@ -1662,14 +1882,14 @@
     </row>
     <row r="7" spans="1:13" ht="99.75" customHeight="1">
       <c r="A7" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="15">
-        <v>4.1500000000000004</v>
+        <v>2.67</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -1679,7 +1899,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>12</v>
@@ -1687,14 +1907,14 @@
     </row>
     <row r="8" spans="1:13" ht="99.75" customHeight="1">
       <c r="A8" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="15">
-        <v>4.1500000000000004</v>
+        <v>2.67</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -1704,7 +1924,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>12</v>
@@ -1712,7 +1932,7 @@
     </row>
     <row r="9" spans="1:13" ht="99.75" customHeight="1">
       <c r="A9" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3">
         <v>10</v>
@@ -1737,7 +1957,7 @@
     </row>
     <row r="10" spans="1:13" ht="99.75" customHeight="1">
       <c r="A10" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
@@ -1762,14 +1982,14 @@
     </row>
     <row r="11" spans="1:13" ht="99.75" customHeight="1">
       <c r="A11" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -1787,14 +2007,14 @@
     </row>
     <row r="12" spans="1:13" ht="99.75" customHeight="1">
       <c r="A12" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -1812,14 +2032,14 @@
     </row>
     <row r="13" spans="1:13" ht="99.75" customHeight="1">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -1829,7 +2049,7 @@
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>12</v>
@@ -1837,14 +2057,14 @@
     </row>
     <row r="14" spans="1:13" ht="99.75" customHeight="1">
       <c r="A14" s="2">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
         <v>10</v>
-      </c>
-      <c r="B14" s="3">
-        <v>20</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="15">
-        <v>9.33</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
@@ -1854,7 +2074,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="10">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>12</v>
@@ -1862,7 +2082,7 @@
     </row>
     <row r="15" spans="1:13" ht="99.75" customHeight="1">
       <c r="A15" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1871,31 +2091,13 @@
       <c r="D15" s="15">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" ref="G15" si="0">D15+E15+F15</f>
-        <v>5.0400000000000009</v>
-      </c>
-      <c r="H15" s="9">
-        <f t="shared" ref="H15:H23" si="1">G15*8</f>
-        <v>40.320000000000007</v>
-      </c>
-      <c r="I15" s="9">
-        <f t="shared" ref="I15:I23" si="2">H15/0.95</f>
-        <v>42.442105263157906</v>
-      </c>
-      <c r="J15" s="9">
-        <f t="shared" ref="J15:J23" si="3">(I15*2)+5</f>
-        <v>89.884210526315812</v>
-      </c>
-      <c r="K15" s="9">
-        <v>95</v>
-      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
       <c r="L15" s="10">
         <v>110</v>
       </c>
@@ -1905,43 +2107,24 @@
     </row>
     <row r="16" spans="1:13" ht="99.75" customHeight="1">
       <c r="A16" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B16" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="5">
-        <v>11.9</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" ref="G16:G23" si="4">D16+E16+F16</f>
-        <v>13.39</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="1"/>
-        <v>107.12</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="2"/>
-        <v>112.75789473684212</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="3"/>
-        <v>230.51578947368424</v>
-      </c>
-      <c r="K16" s="9">
-        <v>230</v>
-      </c>
+      <c r="D16" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
       <c r="L16" s="10">
-        <f t="shared" ref="L16:L23" si="5">K16+10</f>
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>12</v>
@@ -1949,43 +2132,24 @@
     </row>
     <row r="17" spans="1:13" ht="99.75" customHeight="1">
       <c r="A17" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B17" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="5">
-        <v>7.64</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G17" s="8">
-        <f t="shared" si="4"/>
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="H17" s="9">
-        <f t="shared" si="1"/>
-        <v>68.239999999999995</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="2"/>
-        <v>71.831578947368413</v>
-      </c>
-      <c r="J17" s="9">
-        <f t="shared" si="3"/>
-        <v>148.66315789473683</v>
-      </c>
-      <c r="K17" s="9">
-        <v>150</v>
-      </c>
+      <c r="D17" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
       <c r="L17" s="10">
-        <f t="shared" si="5"/>
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>12</v>
@@ -1993,43 +2157,24 @@
     </row>
     <row r="18" spans="1:13" ht="99.75" customHeight="1">
       <c r="A18" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B18" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="5">
-        <v>8.08</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="4"/>
-        <v>10.51</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="1"/>
-        <v>84.08</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="2"/>
-        <v>88.505263157894746</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="3"/>
-        <v>182.01052631578949</v>
-      </c>
-      <c r="K18" s="9">
-        <v>185</v>
-      </c>
+      <c r="D18" s="15">
+        <v>4.74</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
       <c r="L18" s="10">
-        <f t="shared" si="5"/>
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>12</v>
@@ -2037,43 +2182,24 @@
     </row>
     <row r="19" spans="1:13" ht="99.75" customHeight="1">
       <c r="A19" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B19" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="5">
-        <v>4.41</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F19" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
-      </c>
-      <c r="H19" s="9">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
-      </c>
-      <c r="K19" s="9">
-        <v>95</v>
-      </c>
+      <c r="D19" s="15">
+        <v>9.33</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
       <c r="L19" s="10">
-        <f t="shared" si="5"/>
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>12</v>
@@ -2081,14 +2207,14 @@
     </row>
     <row r="20" spans="1:13" ht="99.75" customHeight="1">
       <c r="A20" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B20" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="5">
-        <v>4.41</v>
+      <c r="D20" s="15">
+        <v>4.1500000000000004</v>
       </c>
       <c r="E20" s="6">
         <v>0.7</v>
@@ -2097,27 +2223,26 @@
         <v>0.19</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
+        <f t="shared" ref="G20" si="0">D20+E20+F20</f>
+        <v>5.0400000000000009</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
+        <f t="shared" ref="H20:H28" si="1">G20*8</f>
+        <v>40.320000000000007</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
+        <f t="shared" ref="I20:I28" si="2">H20/0.95</f>
+        <v>42.442105263157906</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
+        <f t="shared" ref="J20:J28" si="3">(I20*2)+5</f>
+        <v>89.884210526315812</v>
       </c>
       <c r="K20" s="9">
         <v>95</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="5"/>
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>12</v>
@@ -2125,14 +2250,14 @@
     </row>
     <row r="21" spans="1:13" ht="99.75" customHeight="1">
       <c r="A21" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B21" s="3">
         <v>25</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5">
-        <v>8.08</v>
+        <v>11.9</v>
       </c>
       <c r="E21" s="6">
         <v>1.17</v>
@@ -2141,27 +2266,27 @@
         <v>0.32</v>
       </c>
       <c r="G21" s="8">
-        <f t="shared" si="4"/>
-        <v>9.57</v>
+        <f t="shared" ref="G21:G28" si="4">D21+E21+F21</f>
+        <v>13.39</v>
       </c>
       <c r="H21" s="9">
         <f t="shared" si="1"/>
-        <v>76.56</v>
+        <v>107.12</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>80.589473684210532</v>
+        <v>112.75789473684212</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="3"/>
-        <v>166.17894736842106</v>
+        <v>230.51578947368424</v>
       </c>
       <c r="K21" s="9">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="5"/>
-        <v>180</v>
+        <f t="shared" ref="L21:L28" si="5">K21+10</f>
+        <v>240</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>12</v>
@@ -2169,14 +2294,14 @@
     </row>
     <row r="22" spans="1:13" ht="99.75" customHeight="1">
       <c r="A22" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B22" s="3">
         <v>15</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5">
-        <v>4.1100000000000003</v>
+        <v>7.64</v>
       </c>
       <c r="E22" s="6">
         <v>0.7</v>
@@ -2186,26 +2311,26 @@
       </c>
       <c r="G22" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="H22" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>68.239999999999995</v>
       </c>
       <c r="I22" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>71.831578947368413</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>148.66315789473683</v>
       </c>
       <c r="K22" s="9">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="L22" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>12</v>
@@ -2213,53 +2338,268 @@
     </row>
     <row r="23" spans="1:13" ht="99.75" customHeight="1">
       <c r="A23" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B23" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="5">
-        <v>4.1100000000000003</v>
+        <v>8.08</v>
       </c>
       <c r="E23" s="6">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F23" s="7">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>10.51</v>
       </c>
       <c r="H23" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>84.08</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>88.505263157894746</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>182.01052631578949</v>
       </c>
       <c r="K23" s="9">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="L23" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A24" s="2">
+        <v>5</v>
+      </c>
+      <c r="B24" s="3">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K24" s="9">
+        <v>95</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A25" s="2">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F25" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" si="4"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K25" s="9">
+        <v>95</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A26" s="2">
+        <v>3</v>
+      </c>
+      <c r="B26" s="3">
+        <v>25</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="G26" s="8">
+        <f t="shared" si="4"/>
+        <v>9.57</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="1"/>
+        <v>76.56</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="2"/>
+        <v>80.589473684210532</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="3"/>
+        <v>166.17894736842106</v>
+      </c>
+      <c r="K26" s="9">
+        <v>170</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A27" s="2">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G27" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K27" s="9">
+        <v>90</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A28" s="2">
+        <v>1</v>
+      </c>
+      <c r="B28" s="3">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K28" s="9">
+        <v>90</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="30" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="31" spans="1:13" ht="15.75" customHeight="1"/>
@@ -2992,33 +3332,43 @@
     <row r="758" ht="15.75" customHeight="1"/>
     <row r="759" ht="15.75" customHeight="1"/>
     <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:M23">
-    <sortCondition descending="1" ref="A16:A23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A21:M28">
+    <sortCondition descending="1" ref="A21:A28"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D23" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D17" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
-    <hyperlink ref="D16" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
-    <hyperlink ref="D15" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
-    <hyperlink ref="D14" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
-    <hyperlink ref="D13" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
-    <hyperlink ref="D12" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
-    <hyperlink ref="D11" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
-    <hyperlink ref="D10" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
-    <hyperlink ref="D9" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
-    <hyperlink ref="D8" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{8C8268C3-6698-451E-835B-5881BC24A1E5}"/>
-    <hyperlink ref="D7" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7798C588-14D3-4699-9A26-5CD4BF185816}"/>
-    <hyperlink ref="D6" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1EB97EDE-E1FA-475A-A341-8A2E05CA1DC0}"/>
-    <hyperlink ref="D5" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FAE6B8A7-EF45-4233-B6B0-CC5A22CEFD2F}"/>
-    <hyperlink ref="D4" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{AB1BE585-CA32-4BAF-9B9B-D69C1EE9D872}"/>
+    <hyperlink ref="D28" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D22" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
+    <hyperlink ref="D21" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
+    <hyperlink ref="D20" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
+    <hyperlink ref="D19" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
+    <hyperlink ref="D18" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
+    <hyperlink ref="D17" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
+    <hyperlink ref="D16" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
+    <hyperlink ref="D15" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
+    <hyperlink ref="D14" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
+    <hyperlink ref="D13" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{8C8268C3-6698-451E-835B-5881BC24A1E5}"/>
+    <hyperlink ref="D12" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7798C588-14D3-4699-9A26-5CD4BF185816}"/>
+    <hyperlink ref="D11" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1EB97EDE-E1FA-475A-A341-8A2E05CA1DC0}"/>
+    <hyperlink ref="D10" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FAE6B8A7-EF45-4233-B6B0-CC5A22CEFD2F}"/>
+    <hyperlink ref="D9" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{AB1BE585-CA32-4BAF-9B9B-D69C1EE9D872}"/>
+    <hyperlink ref="D8" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A86188DB-91B0-425B-BAF4-DE4987E0F1B3}"/>
+    <hyperlink ref="D7" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{EB6126C9-4652-4769-A3A2-872AE269038D}"/>
+    <hyperlink ref="D6" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{26679B4C-8686-4F0B-9342-360252C26495}"/>
+    <hyperlink ref="D5" r:id="rId19" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1C394A94-1F06-4C18-87DC-F739FB993B73}"/>
+    <hyperlink ref="D4" r:id="rId20" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{36A9C58F-499F-476E-9AE9-256170CE45C6}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
-  <drawing r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
--- a/ANILLOS SWA.xlsx
+++ b/ANILLOS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62177D47-6C0C-4C55-855F-C9CDF7B34A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2680915E-0ED8-41F5-802F-3E80976EC05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
   <si>
     <t xml:space="preserve">ANILLOS </t>
   </si>
@@ -343,13 +343,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1209675</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>1133475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -386,13 +386,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1257300</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -429,13 +429,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -472,13 +472,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -515,13 +515,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -558,13 +558,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -601,13 +601,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -644,13 +644,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -687,13 +687,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>257176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>987182</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -731,13 +731,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1142548</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -775,13 +775,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>995408</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -819,13 +819,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>295276</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343026</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1103688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -863,13 +863,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1290246</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1152525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -907,13 +907,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>276224</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362813</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1104899</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -951,13 +951,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1333501</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1000125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -995,13 +995,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1355961</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1104900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1039,13 +1039,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1303022</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1083,13 +1083,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>314326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1333501</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1083688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1127,13 +1127,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85726</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304926</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>910771</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1171,13 +1171,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>981613</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1215,13 +1215,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>166450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1085850</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1200944</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1259,13 +1259,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>323851</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1090589</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1200958</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1303,13 +1303,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>220979</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1005887</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1347,13 +1347,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>1065262</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1391,13 +1391,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>352426</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1009982</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>1200870</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1423,6 +1423,94 @@
         <a:xfrm>
           <a:off x="1828801" y="904874"/>
           <a:ext cx="657556" cy="1086571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>390526</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>86114</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1210421</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Imagen 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{218F5AE9-9611-B4F7-EA94-501F5C825871}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1866901" y="2143514"/>
+          <a:ext cx="638174" cy="1124307"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>428626</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1166018</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Imagen 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53996187-9CBE-1180-B120-8F9001228B51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1905001" y="857251"/>
+          <a:ext cx="619124" cy="1099342"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1731,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:M765"/>
+  <dimension ref="A2:M767"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1807,7 +1895,7 @@
     </row>
     <row r="4" spans="1:13" ht="99.75" customHeight="1">
       <c r="A4" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
@@ -1832,14 +1920,14 @@
     </row>
     <row r="5" spans="1:13" ht="99.75" customHeight="1">
       <c r="A5" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3">
         <v>10</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="15">
-        <v>5.48</v>
+        <v>3.41</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1849,7 +1937,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="10">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>12</v>
@@ -1857,14 +1945,14 @@
     </row>
     <row r="6" spans="1:13" ht="99.75" customHeight="1">
       <c r="A6" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="15">
-        <v>5.48</v>
+        <v>3.41</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1874,7 +1962,7 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>12</v>
@@ -1882,14 +1970,14 @@
     </row>
     <row r="7" spans="1:13" ht="99.75" customHeight="1">
       <c r="A7" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="15">
-        <v>2.67</v>
+        <v>5.48</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -1899,7 +1987,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>12</v>
@@ -1907,14 +1995,14 @@
     </row>
     <row r="8" spans="1:13" ht="99.75" customHeight="1">
       <c r="A8" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="15">
-        <v>2.67</v>
+        <v>5.48</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -1924,7 +2012,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>12</v>
@@ -1932,14 +2020,14 @@
     </row>
     <row r="9" spans="1:13" ht="99.75" customHeight="1">
       <c r="A9" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3">
         <v>10</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="15">
-        <v>4.1500000000000004</v>
+        <v>2.67</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
@@ -1949,7 +2037,7 @@
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="10">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>12</v>
@@ -1957,14 +2045,14 @@
     </row>
     <row r="10" spans="1:13" ht="99.75" customHeight="1">
       <c r="A10" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="15">
-        <v>4.1500000000000004</v>
+        <v>2.67</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
@@ -1974,7 +2062,7 @@
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="10">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>12</v>
@@ -1982,10 +2070,10 @@
     </row>
     <row r="11" spans="1:13" ht="99.75" customHeight="1">
       <c r="A11" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="15">
@@ -1999,7 +2087,7 @@
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>12</v>
@@ -2007,10 +2095,10 @@
     </row>
     <row r="12" spans="1:13" ht="99.75" customHeight="1">
       <c r="A12" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="15">
@@ -2024,7 +2112,7 @@
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>12</v>
@@ -2032,10 +2120,10 @@
     </row>
     <row r="13" spans="1:13" ht="99.75" customHeight="1">
       <c r="A13" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="15">
@@ -2049,7 +2137,7 @@
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>12</v>
@@ -2057,10 +2145,10 @@
     </row>
     <row r="14" spans="1:13" ht="99.75" customHeight="1">
       <c r="A14" s="2">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3">
         <v>15</v>
-      </c>
-      <c r="B14" s="3">
-        <v>10</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="15">
@@ -2074,7 +2162,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>12</v>
@@ -2082,7 +2170,7 @@
     </row>
     <row r="15" spans="1:13" ht="99.75" customHeight="1">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -2107,14 +2195,14 @@
     </row>
     <row r="16" spans="1:13" ht="99.75" customHeight="1">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
         <v>10</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
@@ -2124,7 +2212,7 @@
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>12</v>
@@ -2132,14 +2220,14 @@
     </row>
     <row r="17" spans="1:13" ht="99.75" customHeight="1">
       <c r="A17" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3">
         <v>10</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="15">
-        <v>4.74</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="7"/>
@@ -2149,7 +2237,7 @@
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>12</v>
@@ -2157,7 +2245,7 @@
     </row>
     <row r="18" spans="1:13" ht="99.75" customHeight="1">
       <c r="A18" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -2182,14 +2270,14 @@
     </row>
     <row r="19" spans="1:13" ht="99.75" customHeight="1">
       <c r="A19" s="2">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3">
         <v>10</v>
-      </c>
-      <c r="B19" s="3">
-        <v>20</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="15">
-        <v>9.33</v>
+        <v>4.74</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
@@ -2199,7 +2287,7 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="10">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>12</v>
@@ -2207,42 +2295,24 @@
     </row>
     <row r="20" spans="1:13" ht="99.75" customHeight="1">
       <c r="A20" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B20" s="3">
         <v>10</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="15">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F20" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G20" s="8">
-        <f t="shared" ref="G20" si="0">D20+E20+F20</f>
-        <v>5.0400000000000009</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" ref="H20:H28" si="1">G20*8</f>
-        <v>40.320000000000007</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" ref="I20:I28" si="2">H20/0.95</f>
-        <v>42.442105263157906</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" ref="J20:J28" si="3">(I20*2)+5</f>
-        <v>89.884210526315812</v>
-      </c>
-      <c r="K20" s="9">
-        <v>95</v>
-      </c>
+        <v>4.74</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
       <c r="L20" s="10">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>12</v>
@@ -2250,43 +2320,24 @@
     </row>
     <row r="21" spans="1:13" ht="99.75" customHeight="1">
       <c r="A21" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B21" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="5">
-        <v>11.9</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F21" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" ref="G21:G28" si="4">D21+E21+F21</f>
-        <v>13.39</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="1"/>
-        <v>107.12</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="2"/>
-        <v>112.75789473684212</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="3"/>
-        <v>230.51578947368424</v>
-      </c>
-      <c r="K21" s="9">
-        <v>230</v>
-      </c>
+      <c r="D21" s="15">
+        <v>9.33</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
       <c r="L21" s="10">
-        <f t="shared" ref="L21:L28" si="5">K21+10</f>
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>12</v>
@@ -2294,14 +2345,14 @@
     </row>
     <row r="22" spans="1:13" ht="99.75" customHeight="1">
       <c r="A22" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="5">
-        <v>7.64</v>
+      <c r="D22" s="15">
+        <v>4.1500000000000004</v>
       </c>
       <c r="E22" s="6">
         <v>0.7</v>
@@ -2310,27 +2361,26 @@
         <v>0.19</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" si="4"/>
-        <v>8.5299999999999994</v>
+        <f t="shared" ref="G22" si="0">D22+E22+F22</f>
+        <v>5.0400000000000009</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="1"/>
-        <v>68.239999999999995</v>
+        <f t="shared" ref="H22:H30" si="1">G22*8</f>
+        <v>40.320000000000007</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="2"/>
-        <v>71.831578947368413</v>
+        <f t="shared" ref="I22:I30" si="2">H22/0.95</f>
+        <v>42.442105263157906</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="3"/>
-        <v>148.66315789473683</v>
+        <f t="shared" ref="J22:J30" si="3">(I22*2)+5</f>
+        <v>89.884210526315812</v>
       </c>
       <c r="K22" s="9">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="5"/>
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>12</v>
@@ -2338,43 +2388,43 @@
     </row>
     <row r="23" spans="1:13" ht="99.75" customHeight="1">
       <c r="A23" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B23" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="5">
-        <v>8.08</v>
+        <v>11.9</v>
       </c>
       <c r="E23" s="6">
-        <v>1.9</v>
+        <v>1.17</v>
       </c>
       <c r="F23" s="7">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" si="4"/>
-        <v>10.51</v>
+        <f t="shared" ref="G23:G30" si="4">D23+E23+F23</f>
+        <v>13.39</v>
       </c>
       <c r="H23" s="9">
         <f t="shared" si="1"/>
-        <v>84.08</v>
+        <v>107.12</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>88.505263157894746</v>
+        <v>112.75789473684212</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="3"/>
-        <v>182.01052631578949</v>
+        <v>230.51578947368424</v>
       </c>
       <c r="K23" s="9">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="5"/>
-        <v>195</v>
+        <f t="shared" ref="L23:L30" si="5">K23+10</f>
+        <v>240</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>12</v>
@@ -2382,14 +2432,14 @@
     </row>
     <row r="24" spans="1:13" ht="99.75" customHeight="1">
       <c r="A24" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B24" s="3">
         <v>15</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="5">
-        <v>4.41</v>
+        <v>7.64</v>
       </c>
       <c r="E24" s="6">
         <v>0.7</v>
@@ -2399,26 +2449,26 @@
       </c>
       <c r="G24" s="8">
         <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="H24" s="9">
         <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
+        <v>68.239999999999995</v>
       </c>
       <c r="I24" s="9">
         <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
+        <v>71.831578947368413</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
+        <v>148.66315789473683</v>
       </c>
       <c r="K24" s="9">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="L24" s="10">
         <f t="shared" si="5"/>
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="M24" s="11" t="s">
         <v>12</v>
@@ -2426,43 +2476,43 @@
     </row>
     <row r="25" spans="1:13" ht="99.75" customHeight="1">
       <c r="A25" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B25" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="5">
-        <v>4.41</v>
+        <v>8.08</v>
       </c>
       <c r="E25" s="6">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F25" s="7">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="4"/>
-        <v>5.3000000000000007</v>
+        <v>10.51</v>
       </c>
       <c r="H25" s="9">
         <f t="shared" si="1"/>
-        <v>42.400000000000006</v>
+        <v>84.08</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>44.631578947368432</v>
+        <v>88.505263157894746</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="3"/>
-        <v>94.263157894736864</v>
+        <v>182.01052631578949</v>
       </c>
       <c r="K25" s="9">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="L25" s="10">
         <f t="shared" si="5"/>
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>12</v>
@@ -2470,43 +2520,43 @@
     </row>
     <row r="26" spans="1:13" ht="99.75" customHeight="1">
       <c r="A26" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B26" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5">
-        <v>8.08</v>
+        <v>4.41</v>
       </c>
       <c r="E26" s="6">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="F26" s="7">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="G26" s="8">
         <f t="shared" si="4"/>
-        <v>9.57</v>
+        <v>5.3000000000000007</v>
       </c>
       <c r="H26" s="9">
         <f t="shared" si="1"/>
-        <v>76.56</v>
+        <v>42.400000000000006</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="2"/>
-        <v>80.589473684210532</v>
+        <v>44.631578947368432</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="3"/>
-        <v>166.17894736842106</v>
+        <v>94.263157894736864</v>
       </c>
       <c r="K26" s="9">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="L26" s="10">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>12</v>
@@ -2514,14 +2564,14 @@
     </row>
     <row r="27" spans="1:13" ht="99.75" customHeight="1">
       <c r="A27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3">
         <v>15</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5">
-        <v>4.1100000000000003</v>
+        <v>4.41</v>
       </c>
       <c r="E27" s="6">
         <v>0.7</v>
@@ -2531,26 +2581,26 @@
       </c>
       <c r="G27" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>5.3000000000000007</v>
       </c>
       <c r="H27" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>42.400000000000006</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>44.631578947368432</v>
       </c>
       <c r="J27" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>94.263157894736864</v>
       </c>
       <c r="K27" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L27" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M27" s="11" t="s">
         <v>12</v>
@@ -2558,50 +2608,136 @@
     </row>
     <row r="28" spans="1:13" ht="99.75" customHeight="1">
       <c r="A28" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5">
-        <v>4.1100000000000003</v>
+        <v>8.08</v>
       </c>
       <c r="E28" s="6">
-        <v>0.7</v>
+        <v>1.17</v>
       </c>
       <c r="F28" s="7">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="G28" s="8">
         <f t="shared" si="4"/>
-        <v>5.0000000000000009</v>
+        <v>9.57</v>
       </c>
       <c r="H28" s="9">
         <f t="shared" si="1"/>
-        <v>40.000000000000007</v>
+        <v>76.56</v>
       </c>
       <c r="I28" s="9">
         <f t="shared" si="2"/>
-        <v>42.105263157894747</v>
+        <v>80.589473684210532</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="3"/>
-        <v>89.210526315789494</v>
+        <v>166.17894736842106</v>
       </c>
       <c r="K28" s="9">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="L28" s="10">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A29" s="2">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H29" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J29" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K29" s="9">
+        <v>90</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="99.75" customHeight="1">
+      <c r="A30" s="2">
+        <v>1</v>
+      </c>
+      <c r="B30" s="3">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" si="4"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="1"/>
+        <v>40.000000000000007</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="2"/>
+        <v>42.105263157894747</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="3"/>
+        <v>89.210526315789494</v>
+      </c>
+      <c r="K30" s="9">
+        <v>90</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="32" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
@@ -3337,38 +3473,42 @@
     <row r="763" ht="15.75" customHeight="1"/>
     <row r="764" ht="15.75" customHeight="1"/>
     <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A21:M28">
-    <sortCondition descending="1" ref="A21:A28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A23:M30">
+    <sortCondition descending="1" ref="A23:A30"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D28" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D22" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
-    <hyperlink ref="D21" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
-    <hyperlink ref="D20" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
-    <hyperlink ref="D19" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
-    <hyperlink ref="D18" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
-    <hyperlink ref="D17" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
-    <hyperlink ref="D16" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
-    <hyperlink ref="D15" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
-    <hyperlink ref="D14" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
-    <hyperlink ref="D13" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{8C8268C3-6698-451E-835B-5881BC24A1E5}"/>
-    <hyperlink ref="D12" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7798C588-14D3-4699-9A26-5CD4BF185816}"/>
-    <hyperlink ref="D11" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1EB97EDE-E1FA-475A-A341-8A2E05CA1DC0}"/>
-    <hyperlink ref="D10" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FAE6B8A7-EF45-4233-B6B0-CC5A22CEFD2F}"/>
-    <hyperlink ref="D9" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{AB1BE585-CA32-4BAF-9B9B-D69C1EE9D872}"/>
-    <hyperlink ref="D8" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A86188DB-91B0-425B-BAF4-DE4987E0F1B3}"/>
-    <hyperlink ref="D7" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{EB6126C9-4652-4769-A3A2-872AE269038D}"/>
-    <hyperlink ref="D6" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{26679B4C-8686-4F0B-9342-360252C26495}"/>
-    <hyperlink ref="D5" r:id="rId19" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1C394A94-1F06-4C18-87DC-F739FB993B73}"/>
-    <hyperlink ref="D4" r:id="rId20" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{36A9C58F-499F-476E-9AE9-256170CE45C6}"/>
+    <hyperlink ref="D30" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D24" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E7BE3379-33A4-4A21-93C1-0C0338093FAF}"/>
+    <hyperlink ref="D23" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5353EFD6-A9D9-49B4-9502-B6F5B299E6EA}"/>
+    <hyperlink ref="D22" r:id="rId4" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FDA96277-8260-4B99-9A49-E6038AA3A3CA}"/>
+    <hyperlink ref="D21" r:id="rId5" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{75F6D607-9FB7-4156-9523-07110CE98A3A}"/>
+    <hyperlink ref="D20" r:id="rId6" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9E82464D-9BCE-422A-9E0C-78737E5FBFEE}"/>
+    <hyperlink ref="D19" r:id="rId7" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{71D96391-0BA2-4FA3-A142-B97307335167}"/>
+    <hyperlink ref="D18" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7CD20DBD-BA8B-498B-A7DE-38004C80FC0B}"/>
+    <hyperlink ref="D17" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B7A28FA6-6F25-4B2B-B613-C542E468D0A9}"/>
+    <hyperlink ref="D16" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{06788887-5416-4987-9CA7-F594E1534CCA}"/>
+    <hyperlink ref="D15" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{8C8268C3-6698-451E-835B-5881BC24A1E5}"/>
+    <hyperlink ref="D14" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7798C588-14D3-4699-9A26-5CD4BF185816}"/>
+    <hyperlink ref="D13" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1EB97EDE-E1FA-475A-A341-8A2E05CA1DC0}"/>
+    <hyperlink ref="D12" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{FAE6B8A7-EF45-4233-B6B0-CC5A22CEFD2F}"/>
+    <hyperlink ref="D11" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{AB1BE585-CA32-4BAF-9B9B-D69C1EE9D872}"/>
+    <hyperlink ref="D10" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A86188DB-91B0-425B-BAF4-DE4987E0F1B3}"/>
+    <hyperlink ref="D9" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{EB6126C9-4652-4769-A3A2-872AE269038D}"/>
+    <hyperlink ref="D8" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{26679B4C-8686-4F0B-9342-360252C26495}"/>
+    <hyperlink ref="D7" r:id="rId19" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1C394A94-1F06-4C18-87DC-F739FB993B73}"/>
+    <hyperlink ref="D6" r:id="rId20" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{36A9C58F-499F-476E-9AE9-256170CE45C6}"/>
+    <hyperlink ref="D5" r:id="rId21" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B14B8749-15E9-4EC6-8A68-6457849A1784}"/>
+    <hyperlink ref="D4" r:id="rId22" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F896145-235C-4022-B53F-ECEA12D26459}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId21"/>
-  <drawing r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId23"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>